--- a/data_u1/ae_categories.xlsx
+++ b/data_u1/ae_categories.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sksiafis/Documents/GitHub/LSR3_taar1_H/data_u1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8E98D4-FCB5-3246-85DC-A662B0BDD010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DFFFDE-E6FB-2645-B440-53AD9DF346E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13940" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>headache</t>
   </si>
@@ -146,6 +146,12 @@
   </si>
   <si>
     <t>anticholinergic_symptom</t>
+  </si>
+  <si>
+    <t>Worsening of psychosis</t>
+  </si>
+  <si>
+    <t>psychosis</t>
   </si>
 </sst>
 </file>
@@ -712,67 +718,74 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="5"/>
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="1"/>
     </row>
-    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
     </row>
-    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
     </row>
-    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
     </row>
-    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
     </row>
-    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="5"/>
     </row>
-    <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
     </row>
-    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
     </row>
-    <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
     </row>
-    <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
     </row>
-    <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
     </row>
-    <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
     </row>
-    <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="5"/>
     </row>
     <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
